--- a/CO2BLOCK/example_data.xlsx
+++ b/CO2BLOCK/example_data.xlsx
@@ -1,20 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\CO2 Storage\Analytical solutions\CO2-block\Published versions\Initial on Imperial repo\CO2BLOCK-v2\CO2BLOCK\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{155CBC1A-9158-4B34-9502-6E076D2DFFDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="720" windowWidth="18915" windowHeight="3675"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="example_data" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>Unit name</t>
   </si>
@@ -85,13 +104,19 @@
     <t>tensile strength</t>
   </si>
   <si>
-    <t>example</t>
+    <t>Closed</t>
+  </si>
+  <si>
+    <t>Example open</t>
+  </si>
+  <si>
+    <t>Example closed</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -573,54 +598,56 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
-    <cellStyle name="20% - Énfasis1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - Énfasis2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - Énfasis3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - Énfasis4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - Énfasis5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - Énfasis6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - Énfasis1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - Énfasis2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - Énfasis3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - Énfasis4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - Énfasis5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - Énfasis6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - Énfasis1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - Énfasis2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - Énfasis3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - Énfasis4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - Énfasis5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - Énfasis6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="Buena" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Cálculo" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Celda de comprobación" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Celda vinculada" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="Encabezado 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Énfasis1" xfId="18" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="Énfasis2" xfId="22" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="Énfasis3" xfId="26" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="Énfasis4" xfId="30" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="Énfasis5" xfId="34" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="Énfasis6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Entrada" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Incorrecto" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
     <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Notas" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Salida" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Texto de advertencia" xfId="14" builtinId="11" customBuiltin="1"/>
-    <cellStyle name="Texto explicativo" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Título" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="Título 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Título 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Título 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -628,14 +655,17 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -673,7 +703,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -745,7 +775,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -918,16 +948,33 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:V2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:V3"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="5" max="5" width="18.28515625" customWidth="1"/>
-    <col min="22" max="22" width="15.7109375" customWidth="1"/>
+    <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.21875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="30.88671875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="20.88671875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="24.77734375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -995,51 +1042,93 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="2" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C2" s="2">
-        <v>1300</v>
+        <v>1500</v>
       </c>
       <c r="D2" s="2">
-        <v>2300</v>
+        <v>2000</v>
       </c>
       <c r="E2" s="2">
-        <v>200</v>
-      </c>
-      <c r="F2" s="3">
-        <v>300</v>
+        <v>100</v>
+      </c>
+      <c r="F2" s="2">
+        <v>1000</v>
       </c>
       <c r="G2" s="2">
         <v>100</v>
       </c>
-      <c r="H2" s="3">
-        <v>0.24</v>
-      </c>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
+      <c r="H2" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="I2" s="2">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="J2" s="2">
+        <v>2.9999999999999997E-4</v>
+      </c>
       <c r="N2" s="2">
-        <v>16.600000000000001</v>
-      </c>
-      <c r="O2" s="2"/>
-      <c r="P2" s="2"/>
-      <c r="Q2" s="2">
-        <v>89000</v>
+        <v>15</v>
+      </c>
+      <c r="O2" s="2">
+        <v>20</v>
+      </c>
+      <c r="P2" s="2">
+        <v>50</v>
       </c>
       <c r="R2" s="2">
-        <v>26.3</v>
-      </c>
-      <c r="S2" s="2"/>
-      <c r="T2" s="2"/>
-      <c r="U2" s="2"/>
-      <c r="V2" s="2"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="2">
+        <v>1500</v>
+      </c>
+      <c r="D3" s="2">
+        <v>2000</v>
+      </c>
+      <c r="E3" s="2">
+        <v>100</v>
+      </c>
+      <c r="F3" s="2">
+        <v>1000</v>
+      </c>
+      <c r="G3" s="2">
+        <v>100</v>
+      </c>
+      <c r="H3" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="I3" s="2">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="J3" s="2">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="N3" s="2">
+        <v>15</v>
+      </c>
+      <c r="O3" s="2">
+        <v>20</v>
+      </c>
+      <c r="P3" s="2">
+        <v>50</v>
+      </c>
+      <c r="R3" s="2">
+        <v>50</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
